--- a/Data/matchs.xlsx
+++ b/Data/matchs.xlsx
@@ -788,10 +788,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="J9" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K9" s="0">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="K9" s="0">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>13</x:v>

--- a/Data/matchs.xlsx
+++ b/Data/matchs.xlsx
@@ -112,7 +112,13 @@
     <x:t>Autre équipe</x:t>
   </x:si>
   <x:si>
+    <x:t>81 normandie, repentigny</x:t>
+  </x:si>
+  <x:si>
     <x:t>Scorptin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Président - Kennedy</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -715,7 +721,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>8</x:v>
@@ -753,7 +759,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>13</x:v>
@@ -782,7 +788,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
         <x:v>13</x:v>

--- a/Data/matchs.xlsx
+++ b/Data/matchs.xlsx
@@ -103,6 +103,9 @@
     <x:t>Amitié</x:t>
   </x:si>
   <x:si>
+    <x:t>Président - Kennedy</x:t>
+  </x:si>
+  <x:si>
     <x:t>08:00</x:t>
   </x:si>
   <x:si>
@@ -118,7 +121,16 @@
     <x:t>Scorptin</x:t>
   </x:si>
   <x:si>
-    <x:t>Président - Kennedy</x:t>
+    <x:t>16:29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Patage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdasad</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -545,6 +557,12 @@
       <x:c r="I2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
+      <x:c r="J2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="0">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="L2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -577,6 +595,12 @@
       <x:c r="I3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
+      <x:c r="J3" s="0">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K3" s="0">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -721,7 +745,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>8</x:v>
@@ -744,10 +768,10 @@
         <x:v>46118</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>26</x:v>
@@ -756,10 +780,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>13</x:v>
@@ -788,7 +812,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
         <x:v>13</x:v>
@@ -800,6 +824,38 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:12">
+      <x:c r="A10" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="1">
+        <x:v>46142</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>

--- a/Data/matchs.xlsx
+++ b/Data/matchs.xlsx
@@ -52,85 +52,31 @@
     <x:t>Notes</x:t>
   </x:si>
   <x:si>
-    <x:t>06:05</x:t>
+    <x:t>AdversaireId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les scorpion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frederick-Bach</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>07:05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>true</x:t>
-  </x:si>
-  <x:si>
-    <x:t>St-Jean Vioney</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11:28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>false</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les scorpions</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Note pour le match</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Argonaute</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mascouche</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scorpion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Amitié</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Président - Kennedy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08:30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Autre équipe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81 normandie, repentigny</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scorptin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16:29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Patage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdasad</x:t>
+    <x:t>04:05</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -488,10 +434,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L1"/>
+  <x:dimension ref="A1:M1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:12">
+    <x:row r="1" spans="1:13">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -528,8 +474,11 @@
       <x:c r="L1" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="M1" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:12">
+    <x:row r="2" spans="1:13">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -537,37 +486,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>46114</x:v>
+        <x:v>46128</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="0">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M2" s="0">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:12">
+    <x:row r="3" spans="1:13">
       <x:c r="A3" s="0">
         <x:v>2</x:v>
       </x:c>
@@ -575,25 +521,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>46112</x:v>
+        <x:v>46125</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="I3" s="0" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>22</x:v>
@@ -602,261 +548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:12">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M3" s="0">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="1">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J4" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K4" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:12">
-      <x:c r="A5" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="1">
-        <x:v>46091</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J5" s="0">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:12">
-      <x:c r="A6" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="1">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J6" s="0">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K6" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:12">
-      <x:c r="A7" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="1">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J7" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K7" s="0">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:12">
-      <x:c r="A8" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="1">
-        <x:v>46118</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:12">
-      <x:c r="A9" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="1">
-        <x:v>46106</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J9" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K9" s="0">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:12">
-      <x:c r="A10" s="0">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="1">
-        <x:v>46142</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/matchs.xlsx
+++ b/Data/matchs.xlsx
@@ -53,30 +53,6 @@
   </x:si>
   <x:si>
     <x:t>AdversaireId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10:30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11:30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>false</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les scorpion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Frederick-Bach</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>04:05</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -122,20 +98,13 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -478,82 +447,6 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:13">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="1">
-        <x:v>46128</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="M2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:13">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
-        <x:v>46125</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J3" s="0">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="M3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
